--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,13 +52,151 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-15T18:42:49.869Z</t>
+    <t>2026-04-15T20:47:05.070Z</t>
   </si>
   <si>
     <t>AI Infrastructure, Secure Networking, and Software Solutions - Cisco</t>
   </si>
   <si>
     <t>https://www.cisco.com/</t>
+  </si>
+  <si>
+    <t>site/us/en/products/index.report.json</t>
+  </si>
+  <si>
+    <t>["hero","accordion","columns","columns"]</t>
+  </si>
+  <si>
+    <t>site/us/en/products/index</t>
+  </si>
+  <si>
+    <t>category-hub</t>
+  </si>
+  <si>
+    <t>2026-04-15T18:58:13.284Z</t>
+  </si>
+  <si>
+    <t>Cisco Products: Networking, Security, Data Center - Cisco</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/site/us/en/products/index.html</t>
+  </si>
+  <si>
+    <t>site/us/en/solutions/index.report.json</t>
+  </si>
+  <si>
+    <t>["hero","accordion","columns"]</t>
+  </si>
+  <si>
+    <t>site/us/en/solutions/index</t>
+  </si>
+  <si>
+    <t>2026-04-15T18:58:19.200Z</t>
+  </si>
+  <si>
+    <t>Cisco Solutions for Technology, Industry, and Business Needs - Cisco</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/site/us/en/solutions/index.html</t>
+  </si>
+  <si>
+    <t>site/us/en/about/case-studies-customer-stories/nestle.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>site/us/en/about/case-studies-customer-stories/nestle</t>
+  </si>
+  <si>
+    <t>case-study</t>
+  </si>
+  <si>
+    <t>2026-04-15T19:43:44.173Z</t>
+  </si>
+  <si>
+    <t>Nestlé and Cisco SD-WAN Case Study - Cisco</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/site/us/en/about/case-studies-customer-stories/nestle.html</t>
+  </si>
+  <si>
+    <t>site/us/en/about/why-cisco/index.report.json</t>
+  </si>
+  <si>
+    <t>["columns","columns","columns","columns","cards","cards"]</t>
+  </si>
+  <si>
+    <t>site/us/en/about/why-cisco/index</t>
+  </si>
+  <si>
+    <t>about-corporate</t>
+  </si>
+  <si>
+    <t>2026-04-15T19:00:25.439Z</t>
+  </si>
+  <si>
+    <t>Why Customers Choose Cisco - Cisco</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/site/us/en/about/why-cisco/index.html</t>
+  </si>
+  <si>
+    <t>site/us/en/about/why-cisco/mclaren-racing.report.json</t>
+  </si>
+  <si>
+    <t>["columns"]</t>
+  </si>
+  <si>
+    <t>site/us/en/about/why-cisco/mclaren-racing</t>
+  </si>
+  <si>
+    <t>2026-04-15T19:43:51.563Z</t>
+  </si>
+  <si>
+    <t>Cisco powers the McLaren F1 Team - Cisco</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/site/us/en/about/why-cisco/mclaren-racing.html</t>
+  </si>
+  <si>
+    <t>site/us/en/products/networking/index.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns"]</t>
+  </si>
+  <si>
+    <t>site/us/en/products/networking/index</t>
+  </si>
+  <si>
+    <t>product-category</t>
+  </si>
+  <si>
+    <t>2026-04-15T18:59:31.334Z</t>
+  </si>
+  <si>
+    <t>Cisco Networking Products and Solutions - Cisco</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/site/us/en/products/networking/index.html</t>
+  </si>
+  <si>
+    <t>site/us/en/products/security/index.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns","columns"]</t>
+  </si>
+  <si>
+    <t>site/us/en/products/security/index</t>
+  </si>
+  <si>
+    <t>2026-04-15T18:59:38.123Z</t>
+  </si>
+  <si>
+    <t>Cisco Security Products and Solutions for Cloud and User Protection - Cisco</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/site/us/en/products/security/index.html</t>
   </si>
 </sst>
 </file>
@@ -447,16 +585,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +644,188 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
